--- a/data/comidas.xlsx
+++ b/data/comidas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>comida</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cena</t>
         </is>
       </c>
     </row>
@@ -434,10 +439,11 @@
           <t>Paella de pollo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -446,10 +452,11 @@
           <t>Lentejas con chorizo</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -458,10 +465,11 @@
           <t>Pasta boloñesa</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B4" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -470,10 +478,11 @@
           <t>Tortilla de patatas</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +491,11 @@
           <t>Arroz al horno</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +504,11 @@
           <t>Pollo asado</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -506,10 +517,11 @@
           <t>Ensalada mixta</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -518,10 +530,11 @@
           <t>Gazpacho</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>comida</t>
-        </is>
+      <c r="B9" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -530,10 +543,11 @@
           <t>Crema de calabacín</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -542,10 +556,11 @@
           <t>Huevos revueltos con champiñones</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -554,10 +569,11 @@
           <t>Ensalada de atún</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -566,10 +582,11 @@
           <t>Salmón a la plancha</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -578,10 +595,11 @@
           <t>Croquetas caseras</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -590,10 +608,11 @@
           <t>Verduras a la plancha con huevo</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
